--- a/ツール/加点判定用賃金台帳テンプレート.xlsx
+++ b/ツール/加点判定用賃金台帳テンプレート.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -111,6 +111,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:R26"/>
+  <dimension ref="B1:AE26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -497,6 +500,19 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,7 +541,14 @@
     <row r="4" ht="48" customHeight="1">
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>※時間換算給与＝基本給÷月間所定労働時間（残業・通勤・精皆勤・家族手当を除く所定内賃金で記入）。月列は暦月固定（令和6年10月〜令和7年9月＝加点①、R列＝交付申請直近月＝加点②）。支給がない月は空欄。役員は雇用形態に「役員」と記入（判定母数から除外されます）。</t>
+          <t>※時間換算給与＝基本給÷月間所定労働時間（残業・通勤・精皆勤・家族手当を除く所定内賃金で記入）。月列は暦月固定（令和6年10月〜令和7年9月＝加点①、R列＝交付申請直近月＝加点②）。支給がない月は空欄。役員は雇用形態に「役員」と記入（判定母数から除外されます）。時給制パート等で月により労働時間が変わる場合は S〜AE列に月別労働時間を入力（空欄の月はE列で換算）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>月別労働時間（任意）— 月ごとに変動する場合のみ入力。空欄の月はE列を使用</t>
         </is>
       </c>
     </row>
@@ -627,6 +650,84 @@
         <is>
           <t>交付申請直近月
 基本給</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>令和6年10月
+労働時間</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>令和6年11月
+労働時間</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>令和6年12月
+労働時間</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年1月
+労働時間</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年2月
+労働時間</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年3月
+労働時間</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年4月
+労働時間</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年5月
+労働時間</t>
+        </is>
+      </c>
+      <c r="AA6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年6月
+労働時間</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年7月
+労働時間</t>
+        </is>
+      </c>
+      <c r="AC6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年8月
+労働時間</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年9月
+労働時間</t>
+        </is>
+      </c>
+      <c r="AE6" s="6" t="inlineStr">
+        <is>
+          <t>交付申請直近月
+労働時間</t>
         </is>
       </c>
     </row>
@@ -648,6 +749,19 @@
       <c r="P7" s="7" t="n"/>
       <c r="Q7" s="7" t="n"/>
       <c r="R7" s="7" t="n"/>
+      <c r="S7" s="7" t="n"/>
+      <c r="T7" s="7" t="n"/>
+      <c r="U7" s="7" t="n"/>
+      <c r="V7" s="7" t="n"/>
+      <c r="W7" s="7" t="n"/>
+      <c r="X7" s="7" t="n"/>
+      <c r="Y7" s="7" t="n"/>
+      <c r="Z7" s="7" t="n"/>
+      <c r="AA7" s="7" t="n"/>
+      <c r="AB7" s="7" t="n"/>
+      <c r="AC7" s="7" t="n"/>
+      <c r="AD7" s="7" t="n"/>
+      <c r="AE7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="7" t="n"/>
@@ -667,6 +781,19 @@
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="7" t="n"/>
       <c r="R8" s="7" t="n"/>
+      <c r="S8" s="7" t="n"/>
+      <c r="T8" s="7" t="n"/>
+      <c r="U8" s="7" t="n"/>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="7" t="n"/>
+      <c r="X8" s="7" t="n"/>
+      <c r="Y8" s="7" t="n"/>
+      <c r="Z8" s="7" t="n"/>
+      <c r="AA8" s="7" t="n"/>
+      <c r="AB8" s="7" t="n"/>
+      <c r="AC8" s="7" t="n"/>
+      <c r="AD8" s="7" t="n"/>
+      <c r="AE8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="7" t="n"/>
@@ -686,6 +813,19 @@
       <c r="P9" s="7" t="n"/>
       <c r="Q9" s="7" t="n"/>
       <c r="R9" s="7" t="n"/>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="7" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n"/>
+      <c r="Z9" s="7" t="n"/>
+      <c r="AA9" s="7" t="n"/>
+      <c r="AB9" s="7" t="n"/>
+      <c r="AC9" s="7" t="n"/>
+      <c r="AD9" s="7" t="n"/>
+      <c r="AE9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="7" t="n"/>
@@ -705,6 +845,19 @@
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="7" t="n"/>
       <c r="R10" s="7" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="7" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="7" t="n"/>
+      <c r="W10" s="7" t="n"/>
+      <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="7" t="n"/>
+      <c r="Z10" s="7" t="n"/>
+      <c r="AA10" s="7" t="n"/>
+      <c r="AB10" s="7" t="n"/>
+      <c r="AC10" s="7" t="n"/>
+      <c r="AD10" s="7" t="n"/>
+      <c r="AE10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="7" t="n"/>
@@ -724,6 +877,19 @@
       <c r="P11" s="7" t="n"/>
       <c r="Q11" s="7" t="n"/>
       <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
+      <c r="W11" s="7" t="n"/>
+      <c r="X11" s="7" t="n"/>
+      <c r="Y11" s="7" t="n"/>
+      <c r="Z11" s="7" t="n"/>
+      <c r="AA11" s="7" t="n"/>
+      <c r="AB11" s="7" t="n"/>
+      <c r="AC11" s="7" t="n"/>
+      <c r="AD11" s="7" t="n"/>
+      <c r="AE11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="7" t="n"/>
@@ -743,6 +909,19 @@
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="7" t="n"/>
       <c r="R12" s="7" t="n"/>
+      <c r="S12" s="7" t="n"/>
+      <c r="T12" s="7" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="7" t="n"/>
+      <c r="Z12" s="7" t="n"/>
+      <c r="AA12" s="7" t="n"/>
+      <c r="AB12" s="7" t="n"/>
+      <c r="AC12" s="7" t="n"/>
+      <c r="AD12" s="7" t="n"/>
+      <c r="AE12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="7" t="n"/>
@@ -762,6 +941,19 @@
       <c r="P13" s="7" t="n"/>
       <c r="Q13" s="7" t="n"/>
       <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="n"/>
+      <c r="Y13" s="7" t="n"/>
+      <c r="Z13" s="7" t="n"/>
+      <c r="AA13" s="7" t="n"/>
+      <c r="AB13" s="7" t="n"/>
+      <c r="AC13" s="7" t="n"/>
+      <c r="AD13" s="7" t="n"/>
+      <c r="AE13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="7" t="n"/>
@@ -781,6 +973,19 @@
       <c r="P14" s="7" t="n"/>
       <c r="Q14" s="7" t="n"/>
       <c r="R14" s="7" t="n"/>
+      <c r="S14" s="7" t="n"/>
+      <c r="T14" s="7" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" s="7" t="n"/>
+      <c r="AB14" s="7" t="n"/>
+      <c r="AC14" s="7" t="n"/>
+      <c r="AD14" s="7" t="n"/>
+      <c r="AE14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="7" t="n"/>
@@ -800,6 +1005,19 @@
       <c r="P15" s="7" t="n"/>
       <c r="Q15" s="7" t="n"/>
       <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="7" t="n"/>
+      <c r="AB15" s="7" t="n"/>
+      <c r="AC15" s="7" t="n"/>
+      <c r="AD15" s="7" t="n"/>
+      <c r="AE15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="7" t="n"/>
@@ -819,6 +1037,19 @@
       <c r="P16" s="7" t="n"/>
       <c r="Q16" s="7" t="n"/>
       <c r="R16" s="7" t="n"/>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="7" t="n"/>
+      <c r="X16" s="7" t="n"/>
+      <c r="Y16" s="7" t="n"/>
+      <c r="Z16" s="7" t="n"/>
+      <c r="AA16" s="7" t="n"/>
+      <c r="AB16" s="7" t="n"/>
+      <c r="AC16" s="7" t="n"/>
+      <c r="AD16" s="7" t="n"/>
+      <c r="AE16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="7" t="n"/>
@@ -838,6 +1069,19 @@
       <c r="P17" s="7" t="n"/>
       <c r="Q17" s="7" t="n"/>
       <c r="R17" s="7" t="n"/>
+      <c r="S17" s="7" t="n"/>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
+      <c r="W17" s="7" t="n"/>
+      <c r="X17" s="7" t="n"/>
+      <c r="Y17" s="7" t="n"/>
+      <c r="Z17" s="7" t="n"/>
+      <c r="AA17" s="7" t="n"/>
+      <c r="AB17" s="7" t="n"/>
+      <c r="AC17" s="7" t="n"/>
+      <c r="AD17" s="7" t="n"/>
+      <c r="AE17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="7" t="n"/>
@@ -857,6 +1101,19 @@
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="7" t="n"/>
       <c r="R18" s="7" t="n"/>
+      <c r="S18" s="7" t="n"/>
+      <c r="T18" s="7" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="Z18" s="7" t="n"/>
+      <c r="AA18" s="7" t="n"/>
+      <c r="AB18" s="7" t="n"/>
+      <c r="AC18" s="7" t="n"/>
+      <c r="AD18" s="7" t="n"/>
+      <c r="AE18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="7" t="n"/>
@@ -876,6 +1133,19 @@
       <c r="P19" s="7" t="n"/>
       <c r="Q19" s="7" t="n"/>
       <c r="R19" s="7" t="n"/>
+      <c r="S19" s="7" t="n"/>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="n"/>
+      <c r="Y19" s="7" t="n"/>
+      <c r="Z19" s="7" t="n"/>
+      <c r="AA19" s="7" t="n"/>
+      <c r="AB19" s="7" t="n"/>
+      <c r="AC19" s="7" t="n"/>
+      <c r="AD19" s="7" t="n"/>
+      <c r="AE19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="7" t="n"/>
@@ -895,6 +1165,19 @@
       <c r="P20" s="7" t="n"/>
       <c r="Q20" s="7" t="n"/>
       <c r="R20" s="7" t="n"/>
+      <c r="S20" s="7" t="n"/>
+      <c r="T20" s="7" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="n"/>
+      <c r="Y20" s="7" t="n"/>
+      <c r="Z20" s="7" t="n"/>
+      <c r="AA20" s="7" t="n"/>
+      <c r="AB20" s="7" t="n"/>
+      <c r="AC20" s="7" t="n"/>
+      <c r="AD20" s="7" t="n"/>
+      <c r="AE20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="7" t="n"/>
@@ -914,6 +1197,19 @@
       <c r="P21" s="7" t="n"/>
       <c r="Q21" s="7" t="n"/>
       <c r="R21" s="7" t="n"/>
+      <c r="S21" s="7" t="n"/>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="7" t="n"/>
+      <c r="X21" s="7" t="n"/>
+      <c r="Y21" s="7" t="n"/>
+      <c r="Z21" s="7" t="n"/>
+      <c r="AA21" s="7" t="n"/>
+      <c r="AB21" s="7" t="n"/>
+      <c r="AC21" s="7" t="n"/>
+      <c r="AD21" s="7" t="n"/>
+      <c r="AE21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="7" t="n"/>
@@ -933,6 +1229,19 @@
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="7" t="n"/>
       <c r="R22" s="7" t="n"/>
+      <c r="S22" s="7" t="n"/>
+      <c r="T22" s="7" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="7" t="n"/>
+      <c r="W22" s="7" t="n"/>
+      <c r="X22" s="7" t="n"/>
+      <c r="Y22" s="7" t="n"/>
+      <c r="Z22" s="7" t="n"/>
+      <c r="AA22" s="7" t="n"/>
+      <c r="AB22" s="7" t="n"/>
+      <c r="AC22" s="7" t="n"/>
+      <c r="AD22" s="7" t="n"/>
+      <c r="AE22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="7" t="n"/>
@@ -952,6 +1261,19 @@
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="7" t="n"/>
       <c r="R23" s="7" t="n"/>
+      <c r="S23" s="7" t="n"/>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
+      <c r="W23" s="7" t="n"/>
+      <c r="X23" s="7" t="n"/>
+      <c r="Y23" s="7" t="n"/>
+      <c r="Z23" s="7" t="n"/>
+      <c r="AA23" s="7" t="n"/>
+      <c r="AB23" s="7" t="n"/>
+      <c r="AC23" s="7" t="n"/>
+      <c r="AD23" s="7" t="n"/>
+      <c r="AE23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="7" t="n"/>
@@ -971,6 +1293,19 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="7" t="n"/>
       <c r="R24" s="7" t="n"/>
+      <c r="S24" s="7" t="n"/>
+      <c r="T24" s="7" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="7" t="n"/>
+      <c r="W24" s="7" t="n"/>
+      <c r="X24" s="7" t="n"/>
+      <c r="Y24" s="7" t="n"/>
+      <c r="Z24" s="7" t="n"/>
+      <c r="AA24" s="7" t="n"/>
+      <c r="AB24" s="7" t="n"/>
+      <c r="AC24" s="7" t="n"/>
+      <c r="AD24" s="7" t="n"/>
+      <c r="AE24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="7" t="n"/>
@@ -990,6 +1325,19 @@
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="7" t="n"/>
       <c r="R25" s="7" t="n"/>
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
+      <c r="W25" s="7" t="n"/>
+      <c r="X25" s="7" t="n"/>
+      <c r="Y25" s="7" t="n"/>
+      <c r="Z25" s="7" t="n"/>
+      <c r="AA25" s="7" t="n"/>
+      <c r="AB25" s="7" t="n"/>
+      <c r="AC25" s="7" t="n"/>
+      <c r="AD25" s="7" t="n"/>
+      <c r="AE25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="7" t="n"/>
@@ -1009,10 +1357,24 @@
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="7" t="n"/>
       <c r="R26" s="7" t="n"/>
+      <c r="S26" s="7" t="n"/>
+      <c r="T26" s="7" t="n"/>
+      <c r="U26" s="7" t="n"/>
+      <c r="V26" s="7" t="n"/>
+      <c r="W26" s="7" t="n"/>
+      <c r="X26" s="7" t="n"/>
+      <c r="Y26" s="7" t="n"/>
+      <c r="Z26" s="7" t="n"/>
+      <c r="AA26" s="7" t="n"/>
+      <c r="AB26" s="7" t="n"/>
+      <c r="AC26" s="7" t="n"/>
+      <c r="AD26" s="7" t="n"/>
+      <c r="AE26" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B4:R4"/>
+  <mergeCells count="2">
+    <mergeCell ref="S5:AE5"/>
+    <mergeCell ref="B4:AE4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -1029,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1042,12 +1404,8 @@
           <t>加点判定用賃金台帳 記入ルール</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1123,10 +1481,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>月別労働時間（S〜AE列・任意）</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>月ごとに所定労働時間が変わる場合のみ入力（入力した月はE列より優先、空欄の月はE列を使用）。時給制パートは未入力だと時間換算給与が歪み、最低賃金割れの誤表示につながるため必ず入力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>時間換算給与</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>本台帳には記入不要（ツールが 基本給÷所定労働時間 で自動算出します）。</t>
         </is>
